--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -672,37 +672,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261026억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 262360억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261074억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 258876억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 256251억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 253966억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -936,13 +936,13 @@
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 133억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 134억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 218억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 219억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1971,37 +1971,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261026억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 262360억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261074억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 258876억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 256251억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 253966억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2450,13 +2450,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 133억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 134억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 218억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 219억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6911,20 +6911,20 @@
         <v>0.326745</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.200199</v>
+        <v>0.203955</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.086118</v>
+        <v>0.089439</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.016995</v>
+        <v>0.020046</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.018299</v>
+        <v>-0.015383</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.032005</v>
+        <v>-0.035331</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7060,23 +7060,23 @@
         <v>0.08583200000000001</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.085827</v>
+        <v>0.08583399999999999</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.085827</v>
+        <v>0.085839</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.085837</v>
+        <v>0.08583300000000001</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.085839</v>
+        <v>0.085842</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.085843</v>
+        <v>0.085838</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7215,23 +7215,23 @@
         <v>0.150745</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150756</v>
+        <v>0.150745</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150756</v>
+        <v>0.150738</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150737</v>
+        <v>0.15075</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150735</v>
+        <v>0.150739</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150732</v>
+        <v>0.150748</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7499,13 +7499,13 @@
         <v>4.86</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>6.29</v>
+        <v>6.3</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7954,20 +7954,20 @@
         <v>0.219433</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.219392</v>
+        <v>0.219471</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.21943</v>
+        <v>0.219445</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.219472</v>
+        <v>0.219399</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.219416</v>
+        <v>0.219452</v>
       </c>
       <c r="AN28" s="24" t="n">
         <v>0.219412</v>
@@ -8436,20 +8436,20 @@
         <v>0.250535</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.142957</v>
+        <v>0.14575</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.06900299999999999</v>
+        <v>0.07168099999999999</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.013754</v>
+        <v>0.016181</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.014937</v>
+        <v>-0.012543</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.023977</v>
+        <v>-0.026508</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8689,23 +8689,23 @@
         <v>342.71</v>
       </c>
       <c r="AH34" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AI34" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ34" s="30" t="n"/>
       <c r="AK34" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL34" s="29" t="n">
         <v>342.71</v>
       </c>
       <c r="AM34" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AN34" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AN34" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO34" s="30" t="n"/>
     </row>
@@ -8817,23 +8817,23 @@
         <v>342.71</v>
       </c>
       <c r="AH35" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AI35" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ35" s="30" t="n"/>
       <c r="AK35" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL35" s="29" t="n">
         <v>342.71</v>
       </c>
       <c r="AM35" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AN35" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AN35" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AO35" s="30" t="n"/>
     </row>
@@ -9076,20 +9076,20 @@
         <v>-0.268546</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>-0.297907</v>
+        <v>-0.298418</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>-0.535612</v>
+        <v>-0.537036</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>3.3142</v>
+        <v>3.324583</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>-0.257554</v>
+        <v>-0.25843</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>-0.279708</v>
+        <v>-0.280429</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9204,20 +9204,20 @@
         <v>0.6034620000000001</v>
       </c>
       <c r="AI38" s="24" t="n">
-        <v>0.30538</v>
+        <v>0.305904</v>
       </c>
       <c r="AJ38" s="25" t="n"/>
       <c r="AK38" s="24" t="n">
-        <v>0.295303</v>
+        <v>0.295753</v>
       </c>
       <c r="AL38" s="24" t="n">
-        <v>-0.655097</v>
+        <v>-0.6541670000000001</v>
       </c>
       <c r="AM38" s="24" t="n">
-        <v>0.6367930000000001</v>
+        <v>0.635875</v>
       </c>
       <c r="AN38" s="24" t="n">
-        <v>0.313693</v>
+        <v>0.312791</v>
       </c>
       <c r="AO38" s="25" t="n"/>
     </row>
@@ -9866,16 +9866,16 @@
       </c>
       <c r="AJ44" s="25" t="n"/>
       <c r="AK44" s="24" t="n">
-        <v>-0.054749</v>
+        <v>-0.055866</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>-0.073546</v>
+        <v>-0.074643</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>-0.029782</v>
+        <v>-0.032073</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>-0.008168</v>
+        <v>-0.009335</v>
       </c>
       <c r="AO44" s="25" t="n"/>
     </row>
@@ -10285,23 +10285,23 @@
         <v>0.150745</v>
       </c>
       <c r="AI47" s="24" t="n">
-        <v>0.150756</v>
+        <v>0.150745</v>
       </c>
       <c r="AJ47" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ37,"")</f>
         <v/>
       </c>
       <c r="AK47" s="24" t="n">
-        <v>0.150756</v>
+        <v>0.150738</v>
       </c>
       <c r="AL47" s="24" t="n">
-        <v>0.150737</v>
+        <v>0.15075</v>
       </c>
       <c r="AM47" s="24" t="n">
-        <v>0.150735</v>
+        <v>0.150739</v>
       </c>
       <c r="AN47" s="24" t="n">
-        <v>0.150732</v>
+        <v>0.150748</v>
       </c>
       <c r="AO47" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO37,"")</f>

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$101</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$107</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$93</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 254552억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 255541억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 265726억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 275679억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 287258억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 302650억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 320867억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 340383억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -888,61 +888,61 @@
     <comment ref="AC25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 176억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 176억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 249억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 249억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 313억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 313억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 397억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 397억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 143억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 143억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 229억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 230억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 299억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 302억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 387억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 396억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 134억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 152억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 219억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 251억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1965,43 +1965,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 254552억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255541억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261025억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 265726억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 263179억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 275679억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 261873억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 287258억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 259656억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 302650억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 257012억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 320867억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 253887억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 340383억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2402,61 +2402,61 @@
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 176억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 176억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 249억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 249억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 313억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 313억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 397억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 397억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 143억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 143억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 229억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 230억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 299억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 302억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 387억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 396억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 134억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 152억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 219억 × 6.51% − 총차입금 463억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 251억 × 6.51% − 총차입금 466억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4719,7 +4719,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.1, "op_wape_pct": 51.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 236.66, "rev_act": 287.95, "op_pred": 17.87, "op_act": 48.65}, {"q": "2025Q4", "rev_pred": 287.06, "rev_act": 254.8, "op_pred": 21.68, "op_act": 36.01}, {"q": "2026Q1", "rev_pred": 328.16, "rev_act": 259.87, "op_pred": 24.78, "op_act": 41.62}, {"q": "2026Q2", "rev_pred": 289.52, "rev_act": 318.3, "op_pred": 21.87, "op_act": 51.34}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.1, "op_wape_pct": 51.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 236.66, "rev_act": 287.95, "op_pred": 17.87, "op_act": 48.65}, {"q": "2025Q4", "rev_pred": 287.06, "rev_act": 254.8, "op_pred": 21.68, "op_act": 36.01}, {"q": "2026Q1", "rev_pred": 328.16, "rev_act": 259.87, "op_pred": 24.78, "op_act": 41.62}, {"q": "2026Q2", "rev_pred": 289.52, "rev_act": 318.3, "op_pred": 21.87, "op_act": 51.34}]}</t>
         </is>
       </c>
     </row>
@@ -6905,26 +6905,26 @@
         <v>0.680141</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.462242</v>
+        <v>0.467929</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.326745</v>
+        <v>0.350631</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.203955</v>
+        <v>0.261113</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.089439</v>
+        <v>0.195048</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.020046</v>
+        <v>0.184359</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.015383</v>
+        <v>0.207506</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.035331</v>
+        <v>0.234734</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7054,29 +7054,29 @@
         <v>0.085843</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.08583499999999999</v>
+        <v>0.085845</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.08583200000000001</v>
+        <v>0.085829</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.08583399999999999</v>
+        <v>0.085828</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.085839</v>
+        <v>0.085842</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.08583300000000001</v>
+        <v>0.085836</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.085842</v>
+        <v>0.085829</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.085838</v>
+        <v>0.085831</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7209,29 +7209,29 @@
         <v>0.150752</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150742</v>
+        <v>0.150736</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150745</v>
+        <v>0.150736</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150745</v>
+        <v>0.150746</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150738</v>
+        <v>0.150737</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.15075</v>
+        <v>0.150746</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150739</v>
+        <v>0.150737</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150748</v>
+        <v>0.150753</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7489,23 +7489,23 @@
         <v>2.32</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>6.3</v>
+        <v>6.44</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>3.56</v>
+        <v>4.08</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7948,29 +7948,29 @@
         <v>0.219465</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.219437</v>
+        <v>0.219443</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.219433</v>
+        <v>0.219405</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.219471</v>
+        <v>0.219494</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.219445</v>
+        <v>0.219395</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.219399</v>
+        <v>0.219474</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.219452</v>
+        <v>0.21941</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.219412</v>
+        <v>0.219447</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8433,23 +8433,23 @@
       <c r="AF32" s="31" t="n"/>
       <c r="AG32" s="31" t="n"/>
       <c r="AH32" s="24" t="n">
-        <v>0.250535</v>
+        <v>0.268787</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.14575</v>
+        <v>0.186595</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.07168099999999999</v>
+        <v>0.156261</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.016181</v>
+        <v>0.149556</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>-0.012543</v>
+        <v>0.169364</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>-0.026508</v>
+        <v>0.178141</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8686,10 +8686,10 @@
         <v>-0</v>
       </c>
       <c r="AG34" s="29" t="n">
-        <v>342.71</v>
+        <v>342.7</v>
       </c>
       <c r="AH34" s="29" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AI34" s="29" t="n">
         <v>0</v>
@@ -8699,10 +8699,10 @@
         <v>0</v>
       </c>
       <c r="AL34" s="29" t="n">
-        <v>342.71</v>
+        <v>342.7</v>
       </c>
       <c r="AM34" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN34" s="29" t="n">
         <v>0</v>
@@ -8814,10 +8814,10 @@
         <v>-0</v>
       </c>
       <c r="AG35" s="29" t="n">
-        <v>342.71</v>
+        <v>342.7</v>
       </c>
       <c r="AH35" s="29" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AI35" s="29" t="n">
         <v>0</v>
@@ -8827,10 +8827,10 @@
         <v>0</v>
       </c>
       <c r="AL35" s="29" t="n">
-        <v>342.71</v>
+        <v>342.7</v>
       </c>
       <c r="AM35" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="29" t="n">
         <v>0</v>
@@ -9060,36 +9060,36 @@
         <v/>
       </c>
       <c r="AC37" s="24" t="n">
-        <v>-0.253835</v>
+        <v>-0.251208</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>-0.297684</v>
+        <v>-0.29357</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>-0.558385</v>
+        <v>-0.547464</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>3.828941</v>
+        <v>3.660424</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>-0.268546</v>
+        <v>-0.269352</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>-0.298418</v>
+        <v>-0.303956</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>-0.537036</v>
+        <v>-0.570482</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>3.324583</v>
+        <v>3.452448</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>-0.25843</v>
+        <v>-0.314707</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>-0.280429</v>
+        <v>-0.378247</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9198,26 +9198,26 @@
         <v>0.268258</v>
       </c>
       <c r="AG38" s="24" t="n">
-        <v>-0.64052</v>
+        <v>-0.639991</v>
       </c>
       <c r="AH38" s="24" t="n">
-        <v>0.6034620000000001</v>
+        <v>0.609642</v>
       </c>
       <c r="AI38" s="24" t="n">
-        <v>0.305904</v>
+        <v>0.31228</v>
       </c>
       <c r="AJ38" s="25" t="n"/>
       <c r="AK38" s="24" t="n">
-        <v>0.295753</v>
+        <v>0.310875</v>
       </c>
       <c r="AL38" s="24" t="n">
-        <v>-0.6541670000000001</v>
+        <v>-0.61644</v>
       </c>
       <c r="AM38" s="24" t="n">
-        <v>0.635875</v>
+        <v>0.6522829999999999</v>
       </c>
       <c r="AN38" s="24" t="n">
-        <v>0.312791</v>
+        <v>0.325159</v>
       </c>
       <c r="AO38" s="25" t="n"/>
     </row>
@@ -9856,26 +9856,26 @@
         <v>2.653061</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.6563639999999999</v>
+        <v>0.654545</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>2.370656</v>
+        <v>2.359073</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.731313</v>
+        <v>0.715152</v>
       </c>
       <c r="AJ44" s="25" t="n"/>
       <c r="AK44" s="24" t="n">
-        <v>-0.055866</v>
+        <v>-0.07933</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>-0.074643</v>
+        <v>-0.11978</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>-0.032073</v>
+        <v>-0.110345</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>-0.009335</v>
+        <v>-0.111896</v>
       </c>
       <c r="AO44" s="25" t="n"/>
     </row>
@@ -9994,7 +9994,7 @@
         <v>0</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0</v>
+        <v>-0.012987</v>
       </c>
       <c r="AO45" s="25" t="n"/>
     </row>
@@ -10279,29 +10279,29 @@
         <v>0.150752</v>
       </c>
       <c r="AG47" s="24" t="n">
-        <v>0.150742</v>
+        <v>0.150736</v>
       </c>
       <c r="AH47" s="24" t="n">
-        <v>0.150745</v>
+        <v>0.150736</v>
       </c>
       <c r="AI47" s="24" t="n">
-        <v>0.150745</v>
+        <v>0.150746</v>
       </c>
       <c r="AJ47" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ37,"")</f>
         <v/>
       </c>
       <c r="AK47" s="24" t="n">
-        <v>0.150738</v>
+        <v>0.150737</v>
       </c>
       <c r="AL47" s="24" t="n">
-        <v>0.15075</v>
+        <v>0.150746</v>
       </c>
       <c r="AM47" s="24" t="n">
-        <v>0.150739</v>
+        <v>0.150737</v>
       </c>
       <c r="AN47" s="24" t="n">
-        <v>0.150748</v>
+        <v>0.150753</v>
       </c>
       <c r="AO47" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO37,"")</f>
@@ -10796,7 +10796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO101"/>
+  <dimension ref="A1:AO107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14227,7 +14227,9 @@
       <c r="Z37" s="34" t="n">
         <v>1300</v>
       </c>
-      <c r="AB37" s="5" t="n"/>
+      <c r="AB37" s="19" t="n">
+        <v>300</v>
+      </c>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
       <c r="AE37" s="11" t="n"/>
@@ -15645,7 +15647,7 @@
         <v>61880</v>
       </c>
       <c r="AB53" s="19" t="n">
-        <v>46340</v>
+        <v>46640</v>
       </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
@@ -15731,7 +15733,7 @@
         <v>44057.04</v>
       </c>
       <c r="AB54" s="19" t="n">
-        <v>28696.05</v>
+        <v>28996.05</v>
       </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
@@ -17980,78 +17982,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>2255.31</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>-52133.14</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>47219.46</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>2431.45</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>-1803.73</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>-4285.96</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>-3117.39</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>-1068.55</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>10808.69</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>2068.87</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>8691.620000000001</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>10746.55</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>2700.93</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>5901.77</v>
-      </c>
-      <c r="T85" s="18" t="n">
-        <v>-690.66</v>
-      </c>
-      <c r="U85" s="34" t="n">
-        <v>18658.59</v>
-      </c>
-      <c r="V85" s="18" t="n">
-        <v>-1921.71</v>
-      </c>
-      <c r="W85" s="18" t="n">
-        <v>591.96</v>
-      </c>
-      <c r="X85" s="18" t="n">
-        <v>3954.42</v>
-      </c>
-      <c r="Y85" s="18" t="n">
-        <v>2518.15</v>
-      </c>
-      <c r="Z85" s="34" t="n">
-        <v>5142.82</v>
-      </c>
-      <c r="AA85" s="18" t="n">
-        <v>-9716.469999999999</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
+      <c r="Z85" s="9" t="n"/>
       <c r="AB85" s="19" t="n">
-        <v>-10867.47</v>
+        <v>1036.17</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -18073,38 +18013,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>1731.51</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>1673.07</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>1663.08</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>1617.21</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>1653.98</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>6607.34</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>1522.9</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>1686.86</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
       <c r="P86" s="9" t="n"/>
       <c r="U86" s="9" t="n"/>
       <c r="Z86" s="9" t="n"/>
-      <c r="AB86" s="5" t="n"/>
+      <c r="AB86" s="19" t="n">
+        <v>0.22</v>
+      </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -18125,32 +18044,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>9.68</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>27.17</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
       <c r="P87" s="9" t="n"/>
       <c r="U87" s="9" t="n"/>
       <c r="Z87" s="9" t="n"/>
-      <c r="AB87" s="5" t="n"/>
+      <c r="AB87" s="19" t="n">
+        <v>390.82</v>
+      </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
@@ -18171,50 +18075,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
+          <t>파생상품이익</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="n"/>
+      <c r="K88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
+      <c r="U88" s="9" t="n"/>
+      <c r="Z88" s="9" t="n"/>
+      <c r="AB88" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="F88" s="9" t="n"/>
-      <c r="G88" s="18" t="n">
-        <v>-50701.94</v>
-      </c>
-      <c r="H88" s="18" t="n">
-        <v>50708.39</v>
-      </c>
-      <c r="I88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="34" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="N88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="9" t="n"/>
-      <c r="S88" s="18" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="T88" s="18" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="U88" s="9" t="n"/>
-      <c r="X88" s="18" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Y88" s="18" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z88" s="9" t="n"/>
-      <c r="AB88" s="5" t="n"/>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -18235,78 +18106,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>26.51</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="G89" s="18" t="n">
-        <v>-5765.74</v>
-      </c>
-      <c r="H89" s="18" t="n">
-        <v>-6935.63</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>-465.49</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>-28.76</v>
-      </c>
-      <c r="K89" s="34" t="n">
-        <v>-13195.62</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>-503.93</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>-532.01</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>-238.34</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>-507.45</v>
-      </c>
-      <c r="P89" s="34" t="n">
-        <v>-1781.73</v>
-      </c>
-      <c r="Q89" s="18" t="n">
-        <v>194.09</v>
-      </c>
-      <c r="R89" s="18" t="n">
-        <v>227.11</v>
-      </c>
-      <c r="S89" s="18" t="n">
-        <v>-130.28</v>
-      </c>
-      <c r="T89" s="18" t="n">
-        <v>-87.73</v>
-      </c>
-      <c r="U89" s="34" t="n">
-        <v>203.19</v>
-      </c>
-      <c r="V89" s="18" t="n">
-        <v>-4969.31</v>
-      </c>
-      <c r="W89" s="18" t="n">
-        <v>-5781.45</v>
-      </c>
-      <c r="X89" s="18" t="n">
-        <v>-2670.21</v>
-      </c>
-      <c r="Y89" s="18" t="n">
-        <v>-2451.87</v>
-      </c>
-      <c r="Z89" s="34" t="n">
-        <v>-15872.84</v>
-      </c>
-      <c r="AA89" s="18" t="n">
-        <v>-15750.1</v>
-      </c>
+      <c r="K89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
+      <c r="U89" s="9" t="n"/>
+      <c r="Z89" s="9" t="n"/>
       <c r="AB89" s="19" t="n">
-        <v>-18964.15</v>
+        <v>0</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -18328,78 +18137,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>8275.57</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="18" t="n">
-        <v>51253.13</v>
-      </c>
-      <c r="H90" s="18" t="n">
-        <v>-45400.28</v>
-      </c>
-      <c r="I90" s="18" t="n">
-        <v>-25627.81</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>-5568.53</v>
-      </c>
-      <c r="K90" s="34" t="n">
-        <v>-25343.49</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>1953.38</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>-970.95</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>3076.65</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>16493.94</v>
-      </c>
-      <c r="P90" s="34" t="n">
-        <v>20553.02</v>
-      </c>
-      <c r="Q90" s="18" t="n">
-        <v>10494.36</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>-28735.1</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>-1253.2</v>
-      </c>
-      <c r="T90" s="18" t="n">
-        <v>4722.66</v>
-      </c>
-      <c r="U90" s="34" t="n">
-        <v>-14771.28</v>
-      </c>
-      <c r="V90" s="18" t="n">
-        <v>28602.1</v>
-      </c>
-      <c r="W90" s="18" t="n">
-        <v>24914.97</v>
-      </c>
-      <c r="X90" s="18" t="n">
-        <v>20132.92</v>
-      </c>
-      <c r="Y90" s="18" t="n">
-        <v>6679.73</v>
-      </c>
-      <c r="Z90" s="34" t="n">
-        <v>80329.72</v>
-      </c>
-      <c r="AA90" s="18" t="n">
-        <v>12579.28</v>
-      </c>
+      <c r="K90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
+      <c r="U90" s="9" t="n"/>
+      <c r="Z90" s="9" t="n"/>
       <c r="AB90" s="19" t="n">
-        <v>33171.11</v>
+        <v>645.35</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -18421,66 +18168,79 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0.82</v>
+        <v>2255.31</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>26.55</v>
+        <v>-52133.14</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>0</v>
+        <v>47219.46</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>0</v>
+        <v>2431.45</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>3.63</v>
+        <v>-1803.73</v>
       </c>
       <c r="K91" s="34" t="n">
-        <v>30.18</v>
+        <v>-4285.96</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>4.55</v>
+        <v>-3117.39</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1068.55</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>215.26</v>
+        <v>10808.69</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>0</v>
+        <v>2068.87</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>220.62</v>
+        <v>8691.620000000001</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>89</v>
+        <v>10746.55</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>0</v>
+        <v>2700.93</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>1</v>
+        <v>5901.77</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>0</v>
+        <v>-690.66</v>
       </c>
       <c r="U91" s="34" t="n">
-        <v>90</v>
+        <v>18658.59</v>
+      </c>
+      <c r="V91" s="18" t="n">
+        <v>-1921.71</v>
+      </c>
+      <c r="W91" s="18" t="n">
+        <v>591.96</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>25</v>
+        <v>3954.42</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="9" t="n"/>
-      <c r="AB91" s="5" t="n"/>
+        <v>2518.15</v>
+      </c>
+      <c r="Z91" s="34" t="n">
+        <v>5142.82</v>
+      </c>
+      <c r="AA91" s="18" t="n">
+        <v>-9716.469999999999</v>
+      </c>
+      <c r="AB91" s="19" t="n">
+        <v>-10867.47</v>
+      </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -18501,79 +18261,38 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>1053.5</v>
+        <v>1731.51</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>391.32</v>
+        <v>1673.07</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>349.23</v>
+        <v>1663.08</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>241.36</v>
+        <v>1617.21</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>973.54</v>
+        <v>1653.98</v>
       </c>
       <c r="K92" s="34" t="n">
-        <v>1955.45</v>
+        <v>6607.34</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>604.6</v>
+        <v>1522.9</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>493.25</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>770.87</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>664.28</v>
-      </c>
-      <c r="P92" s="34" t="n">
-        <v>2533</v>
-      </c>
-      <c r="Q92" s="18" t="n">
-        <v>434.15</v>
-      </c>
-      <c r="R92" s="18" t="n">
-        <v>906.65</v>
-      </c>
-      <c r="S92" s="18" t="n">
-        <v>961.54</v>
-      </c>
-      <c r="T92" s="18" t="n">
-        <v>548.45</v>
-      </c>
-      <c r="U92" s="34" t="n">
-        <v>2850.79</v>
-      </c>
-      <c r="V92" s="18" t="n">
-        <v>1900.29</v>
-      </c>
-      <c r="W92" s="18" t="n">
-        <v>1098.41</v>
-      </c>
-      <c r="X92" s="18" t="n">
-        <v>904.42</v>
-      </c>
-      <c r="Y92" s="18" t="n">
-        <v>2627.7</v>
-      </c>
-      <c r="Z92" s="34" t="n">
-        <v>6530.82</v>
-      </c>
-      <c r="AA92" s="18" t="n">
-        <v>329.53</v>
-      </c>
-      <c r="AB92" s="19" t="n">
-        <v>286.8</v>
-      </c>
+        <v>1686.86</v>
+      </c>
+      <c r="P92" s="9" t="n"/>
+      <c r="U92" s="9" t="n"/>
+      <c r="Z92" s="9" t="n"/>
+      <c r="AB92" s="5" t="n"/>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -18594,79 +18313,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>1053.5</v>
+        <v>9.68</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>398.32</v>
+        <v>10.03</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>349.23</v>
+        <v>10.03</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>242.81</v>
+        <v>4.93</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>974.1</v>
+        <v>2.18</v>
       </c>
       <c r="K93" s="34" t="n">
-        <v>1964.46</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>634.6</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>493.25</v>
-      </c>
-      <c r="N93" s="18" t="n">
-        <v>770.87</v>
-      </c>
-      <c r="O93" s="18" t="n">
-        <v>664.28</v>
-      </c>
-      <c r="P93" s="34" t="n">
-        <v>2563</v>
-      </c>
-      <c r="Q93" s="18" t="n">
-        <v>434.15</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>906.65</v>
-      </c>
-      <c r="S93" s="18" t="n">
-        <v>961.54</v>
-      </c>
-      <c r="T93" s="18" t="n">
-        <v>548.45</v>
-      </c>
-      <c r="U93" s="34" t="n">
-        <v>2850.79</v>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>1900.29</v>
-      </c>
-      <c r="W93" s="18" t="n">
-        <v>1098.41</v>
-      </c>
-      <c r="X93" s="18" t="n">
-        <v>904.42</v>
-      </c>
-      <c r="Y93" s="18" t="n">
-        <v>2627.7</v>
-      </c>
-      <c r="Z93" s="34" t="n">
-        <v>6530.82</v>
-      </c>
-      <c r="AA93" s="18" t="n">
-        <v>329.53</v>
-      </c>
-      <c r="AB93" s="19" t="n">
-        <v>694.8</v>
-      </c>
+        <v>27.17</v>
+      </c>
+      <c r="P93" s="9" t="n"/>
+      <c r="U93" s="9" t="n"/>
+      <c r="Z93" s="9" t="n"/>
+      <c r="AB93" s="5" t="n"/>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="11" t="n"/>
@@ -18687,79 +18359,50 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>866.83</v>
+        <v>0</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="18" t="n">
-        <v>-473.63</v>
+        <v>-50701.94</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>16636.59</v>
+        <v>50708.39</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>-3154.16</v>
+        <v>0</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>-8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="K94" s="34" t="n">
-        <v>13000.76</v>
-      </c>
-      <c r="L94" s="18" t="n">
-        <v>-865.17</v>
-      </c>
-      <c r="M94" s="18" t="n">
-        <v>-184.24</v>
+        <v>6.45</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>2136.46</v>
+        <v>0</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>-12785.74</v>
-      </c>
-      <c r="P94" s="34" t="n">
-        <v>-11698.69</v>
-      </c>
-      <c r="Q94" s="18" t="n">
-        <v>-25435.26</v>
-      </c>
-      <c r="R94" s="18" t="n">
-        <v>11873.43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P94" s="9" t="n"/>
       <c r="S94" s="18" t="n">
-        <v>-1923.63</v>
+        <v>0.09</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>-4828.82</v>
-      </c>
-      <c r="U94" s="34" t="n">
-        <v>-20314.28</v>
-      </c>
-      <c r="V94" s="18" t="n">
-        <v>-10442.3</v>
-      </c>
-      <c r="W94" s="18" t="n">
-        <v>-33307.48</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="U94" s="9" t="n"/>
       <c r="X94" s="18" t="n">
-        <v>-24774.31</v>
+        <v>0.11</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>-12007.03</v>
-      </c>
-      <c r="Z94" s="34" t="n">
-        <v>-80531.12</v>
-      </c>
-      <c r="AA94" s="18" t="n">
-        <v>-3296.81</v>
-      </c>
-      <c r="AB94" s="19" t="n">
-        <v>-22445.04</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="Z94" s="9" t="n"/>
+      <c r="AB94" s="5" t="n"/>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -18780,78 +18423,78 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
-        <v>19.85</v>
+        <v>26.51</v>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="18" t="n">
-        <v>2459.85</v>
+        <v>-5765.74</v>
       </c>
       <c r="H95" s="18" t="n">
-        <v>2319.85</v>
+        <v>-6935.63</v>
       </c>
       <c r="I95" s="18" t="n">
-        <v>5599.85</v>
+        <v>-465.49</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>719.85</v>
+        <v>-28.76</v>
       </c>
       <c r="K95" s="34" t="n">
-        <v>11099.4</v>
+        <v>-13195.62</v>
       </c>
       <c r="L95" s="18" t="n">
-        <v>1019.85</v>
+        <v>-503.93</v>
       </c>
       <c r="M95" s="18" t="n">
-        <v>10019.85</v>
+        <v>-532.01</v>
       </c>
       <c r="N95" s="18" t="n">
-        <v>1139.85</v>
+        <v>-238.34</v>
       </c>
       <c r="O95" s="18" t="n">
-        <v>26319.85</v>
+        <v>-507.45</v>
       </c>
       <c r="P95" s="34" t="n">
-        <v>38499.4</v>
+        <v>-1781.73</v>
       </c>
       <c r="Q95" s="18" t="n">
-        <v>15016.95</v>
+        <v>194.09</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>39016.95</v>
+        <v>227.11</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>25300</v>
+        <v>-130.28</v>
       </c>
       <c r="T95" s="18" t="n">
-        <v>24000</v>
+        <v>-87.73</v>
       </c>
       <c r="U95" s="34" t="n">
-        <v>103333.9</v>
+        <v>203.19</v>
       </c>
       <c r="V95" s="18" t="n">
-        <v>10000</v>
+        <v>-4969.31</v>
       </c>
       <c r="W95" s="18" t="n">
-        <v>25500</v>
+        <v>-5781.45</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>15650</v>
+        <v>-2670.21</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>12000</v>
+        <v>-2451.87</v>
       </c>
       <c r="Z95" s="34" t="n">
-        <v>63150</v>
+        <v>-15872.84</v>
       </c>
       <c r="AA95" s="18" t="n">
-        <v>500</v>
+        <v>-15750.1</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>15540</v>
+        <v>-18964.15</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -18873,78 +18516,78 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E96" s="18" t="n">
-        <v>22778.58</v>
+        <v>8275.57</v>
       </c>
       <c r="F96" s="9" t="n"/>
       <c r="G96" s="18" t="n">
-        <v>-2690.27</v>
+        <v>51253.13</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>36903.52</v>
+        <v>-45400.28</v>
       </c>
       <c r="I96" s="18" t="n">
-        <v>-52634.9</v>
+        <v>-25627.81</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>-14858.29</v>
+        <v>-5568.53</v>
       </c>
       <c r="K96" s="34" t="n">
-        <v>-33279.94</v>
+        <v>-25343.49</v>
       </c>
       <c r="L96" s="18" t="n">
-        <v>-3996.64</v>
+        <v>1953.38</v>
       </c>
       <c r="M96" s="18" t="n">
-        <v>-4602.95</v>
+        <v>-970.95</v>
       </c>
       <c r="N96" s="18" t="n">
-        <v>32049.1</v>
+        <v>3076.65</v>
       </c>
       <c r="O96" s="18" t="n">
-        <v>11597.34</v>
+        <v>16493.94</v>
       </c>
       <c r="P96" s="34" t="n">
-        <v>35046.85</v>
+        <v>20553.02</v>
       </c>
       <c r="Q96" s="18" t="n">
-        <v>-8456.110000000001</v>
+        <v>10494.36</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>-28394.71</v>
+        <v>-28735.1</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>5625.36</v>
+        <v>-1253.2</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>-1533.83</v>
+        <v>4722.66</v>
       </c>
       <c r="U96" s="34" t="n">
-        <v>-32759.29</v>
+        <v>-14771.28</v>
       </c>
       <c r="V96" s="18" t="n">
-        <v>32531.85</v>
+        <v>28602.1</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>-15683.99</v>
+        <v>24914.97</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>-1342.55</v>
+        <v>20132.92</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>-10623.48</v>
+        <v>6679.73</v>
       </c>
       <c r="Z96" s="34" t="n">
-        <v>4881.83</v>
+        <v>80329.72</v>
       </c>
       <c r="AA96" s="18" t="n">
-        <v>-364.42</v>
+        <v>12579.28</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>-179.01</v>
+        <v>33171.11</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -18966,79 +18609,66 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
-        <v>11380.85</v>
+        <v>0.82</v>
       </c>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="18" t="n">
-        <v>27451.56</v>
+        <v>26.55</v>
       </c>
       <c r="H97" s="18" t="n">
-        <v>18447.77</v>
+        <v>0</v>
       </c>
       <c r="I97" s="18" t="n">
-        <v>-26284.37</v>
+        <v>0</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>-7478</v>
+        <v>3.63</v>
       </c>
       <c r="K97" s="34" t="n">
-        <v>12136.96</v>
+        <v>30.18</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>10169.51</v>
+        <v>4.55</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>-2379.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>16027.31</v>
+        <v>215.26</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>5820.27</v>
+        <v>0</v>
       </c>
       <c r="P97" s="34" t="n">
-        <v>29637.86</v>
+        <v>220.62</v>
       </c>
       <c r="Q97" s="18" t="n">
-        <v>25376.1</v>
+        <v>89</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>-14233.97</v>
+        <v>0</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>2900.42</v>
+        <v>1</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>-737</v>
+        <v>0</v>
       </c>
       <c r="U97" s="34" t="n">
-        <v>13305.55</v>
-      </c>
-      <c r="V97" s="18" t="n">
-        <v>29599.31</v>
-      </c>
-      <c r="W97" s="18" t="n">
-        <v>-7883.43</v>
+        <v>90</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>-655.6</v>
+        <v>25</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>-2872.9</v>
-      </c>
-      <c r="Z97" s="34" t="n">
-        <v>18187.38</v>
-      </c>
-      <c r="AA97" s="18" t="n">
-        <v>17822.96</v>
-      </c>
-      <c r="AB97" s="19" t="n">
-        <v>-179.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z97" s="9" t="n"/>
+      <c r="AB97" s="5" t="n"/>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
       <c r="AE97" s="11" t="n"/>
@@ -19059,49 +18689,79 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>1053.5</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="18" t="n">
-        <v>7</v>
+        <v>391.32</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>0</v>
+        <v>349.23</v>
       </c>
       <c r="I98" s="18" t="n">
-        <v>1.45</v>
+        <v>241.36</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>973.54</v>
       </c>
       <c r="K98" s="34" t="n">
-        <v>9.01</v>
+        <v>1955.45</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>30</v>
+        <v>604.6</v>
       </c>
       <c r="M98" s="18" t="n">
-        <v>0</v>
+        <v>493.25</v>
       </c>
       <c r="N98" s="18" t="n">
-        <v>0</v>
+        <v>770.87</v>
       </c>
       <c r="O98" s="18" t="n">
-        <v>0</v>
+        <v>664.28</v>
       </c>
       <c r="P98" s="34" t="n">
-        <v>30</v>
+        <v>2533</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>434.15</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>906.65</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>0</v>
+        <v>961.54</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n"/>
-      <c r="Z98" s="9" t="n"/>
-      <c r="AB98" s="5" t="n"/>
+        <v>548.45</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>2850.79</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>1900.29</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>1098.41</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>904.42</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>2627.7</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>6530.82</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>329.53</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>286.8</v>
+      </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
       <c r="AE98" s="11" t="n"/>
@@ -19122,50 +18782,78 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>1053.5</v>
       </c>
       <c r="F99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>349.23</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>242.81</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>974.1</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>1964.46</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>634.6</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>493.25</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>770.87</v>
+      </c>
       <c r="O99" s="18" t="n">
-        <v>651.12</v>
-      </c>
-      <c r="P99" s="9" t="n"/>
+        <v>664.28</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>2563</v>
+      </c>
       <c r="Q99" s="18" t="n">
-        <v>314.74</v>
+        <v>434.15</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>398.92</v>
+        <v>906.65</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>356.34</v>
+        <v>961.54</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>247.38</v>
+        <v>548.45</v>
       </c>
       <c r="U99" s="34" t="n">
-        <v>1317.38</v>
+        <v>2850.79</v>
       </c>
       <c r="V99" s="18" t="n">
-        <v>1091.29</v>
+        <v>1900.29</v>
       </c>
       <c r="W99" s="18" t="n">
-        <v>379.54</v>
+        <v>1098.41</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>1326.55</v>
+        <v>904.42</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>298.75</v>
+        <v>2627.7</v>
       </c>
       <c r="Z99" s="34" t="n">
-        <v>3096.13</v>
+        <v>6530.82</v>
       </c>
       <c r="AA99" s="18" t="n">
-        <v>2877.74</v>
+        <v>329.53</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>573.55</v>
+        <v>694.8</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -19187,35 +18875,79 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>866.83</v>
       </c>
       <c r="F100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
-      <c r="P100" s="9" t="n"/>
+      <c r="G100" s="18" t="n">
+        <v>-473.63</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>16636.59</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>-3154.16</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="K100" s="34" t="n">
+        <v>13000.76</v>
+      </c>
+      <c r="L100" s="18" t="n">
+        <v>-865.17</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>-184.24</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>2136.46</v>
+      </c>
+      <c r="O100" s="18" t="n">
+        <v>-12785.74</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>-11698.69</v>
+      </c>
       <c r="Q100" s="18" t="n">
-        <v>20457.46</v>
+        <v>-25435.26</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>0.8</v>
+        <v>11873.43</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>0</v>
+        <v>-1923.63</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>0</v>
+        <v>-4828.82</v>
       </c>
       <c r="U100" s="34" t="n">
-        <v>20458.26</v>
+        <v>-20314.28</v>
+      </c>
+      <c r="V100" s="18" t="n">
+        <v>-10442.3</v>
+      </c>
+      <c r="W100" s="18" t="n">
+        <v>-33307.48</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>9232.879999999999</v>
+        <v>-24774.31</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="9" t="n"/>
-      <c r="AB100" s="5" t="n"/>
+        <v>-12007.03</v>
+      </c>
+      <c r="Z100" s="34" t="n">
+        <v>-80531.12</v>
+      </c>
+      <c r="AA100" s="18" t="n">
+        <v>-3296.81</v>
+      </c>
+      <c r="AB100" s="19" t="n">
+        <v>-22445.04</v>
+      </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
       <c r="AE100" s="11" t="n"/>
@@ -19236,19 +18968,78 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
+          <t>차입금의감소</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>19.85</v>
       </c>
       <c r="F101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
-      <c r="P101" s="9" t="n"/>
-      <c r="U101" s="9" t="n"/>
-      <c r="Z101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>2459.85</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>2319.85</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>5599.85</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>719.85</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>11099.4</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>1019.85</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>10019.85</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>1139.85</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>26319.85</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>38499.4</v>
+      </c>
+      <c r="Q101" s="18" t="n">
+        <v>15016.95</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>39016.95</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>25300</v>
+      </c>
+      <c r="T101" s="18" t="n">
+        <v>24000</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>103333.9</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>25500</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>15650</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>63150</v>
+      </c>
       <c r="AA101" s="18" t="n">
-        <v>7.78</v>
+        <v>500</v>
       </c>
       <c r="AB101" s="19" t="n">
-        <v>7.92</v>
+        <v>15540</v>
       </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
@@ -19263,6 +19054,403 @@
       <c r="AM101" s="10" t="n"/>
       <c r="AN101" s="10" t="n"/>
       <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>22778.58</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>-2690.27</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>36903.52</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>-52634.9</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>-14858.29</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>-33279.94</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>-3996.64</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>-4602.95</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>32049.1</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>11597.34</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>35046.85</v>
+      </c>
+      <c r="Q102" s="18" t="n">
+        <v>-8456.110000000001</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>-28394.71</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>5625.36</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>-1533.83</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>-32759.29</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>32531.85</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>-15683.99</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>-1342.55</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>-10623.48</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>4881.83</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>-364.42</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>-179.01</v>
+      </c>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>11380.85</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>27451.56</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>18447.77</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>-26284.37</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>-7478</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>12136.96</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>10169.51</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>-2379.23</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>16027.31</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>5820.27</v>
+      </c>
+      <c r="P103" s="34" t="n">
+        <v>29637.86</v>
+      </c>
+      <c r="Q103" s="18" t="n">
+        <v>25376.1</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>-14233.97</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>2900.42</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>-737</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>13305.55</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>29599.31</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>-7883.43</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>-655.6</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>-2872.9</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>18187.38</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>17822.96</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>-179.01</v>
+      </c>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J104" s="18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K104" s="34" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="L104" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="M104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="S104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="9" t="n"/>
+      <c r="Z104" s="9" t="n"/>
+      <c r="AB104" s="5" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+      <c r="O105" s="18" t="n">
+        <v>651.12</v>
+      </c>
+      <c r="P105" s="9" t="n"/>
+      <c r="Q105" s="18" t="n">
+        <v>314.74</v>
+      </c>
+      <c r="R105" s="18" t="n">
+        <v>398.92</v>
+      </c>
+      <c r="S105" s="18" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="T105" s="18" t="n">
+        <v>247.38</v>
+      </c>
+      <c r="U105" s="34" t="n">
+        <v>1317.38</v>
+      </c>
+      <c r="V105" s="18" t="n">
+        <v>1091.29</v>
+      </c>
+      <c r="W105" s="18" t="n">
+        <v>379.54</v>
+      </c>
+      <c r="X105" s="18" t="n">
+        <v>1326.55</v>
+      </c>
+      <c r="Y105" s="18" t="n">
+        <v>298.75</v>
+      </c>
+      <c r="Z105" s="34" t="n">
+        <v>3096.13</v>
+      </c>
+      <c r="AA105" s="18" t="n">
+        <v>2877.74</v>
+      </c>
+      <c r="AB105" s="19" t="n">
+        <v>573.55</v>
+      </c>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+      <c r="P106" s="9" t="n"/>
+      <c r="Q106" s="18" t="n">
+        <v>20457.46</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>20458.26</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>9232.879999999999</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="9" t="n"/>
+      <c r="AB106" s="5" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="10" t="n"/>
+      <c r="AL106" s="10" t="n"/>
+      <c r="AM106" s="10" t="n"/>
+      <c r="AN106" s="10" t="n"/>
+      <c r="AO106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="n"/>
+      <c r="K107" s="9" t="n"/>
+      <c r="P107" s="9" t="n"/>
+      <c r="U107" s="9" t="n"/>
+      <c r="Z107" s="9" t="n"/>
+      <c r="AA107" s="18" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="AB107" s="19" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="10" t="n"/>
+      <c r="AL107" s="10" t="n"/>
+      <c r="AM107" s="10" t="n"/>
+      <c r="AN107" s="10" t="n"/>
+      <c r="AO107" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19523,7 +19711,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30043,7 +30231,7 @@
         <v>82.17</v>
       </c>
       <c r="AG20" s="20" t="n">
-        <v>86.52</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="AH20" s="20">
         <f>IFERROR(AC20*(1+변수!AH32),"")</f>
@@ -41143,7 +41331,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>676.2</v>
+        <v>676.7</v>
       </c>
     </row>
     <row r="30">
@@ -41163,7 +41351,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="32">
@@ -41213,7 +41401,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.47</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 253980억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 253964억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 263158억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 263123억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 272093억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 272040억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283204억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283133억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 298569억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 298498억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 316779억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 316710억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 336299억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 336233억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1722,43 +1722,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 253980억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 253964억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 263158억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 263123억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 272093억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 272040억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283204억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283133억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 298569억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 298498억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 316779억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 316710억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 336299억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 336233억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4364,7 +4364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5235,35 +5235,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5354,35 +5354,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5592,35 +5592,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5711,35 +5711,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5830,35 +5830,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5949,35 +5949,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6068,35 +6068,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6203,7 +6203,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6410</v>
+        <v>6270</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6476,7 +6476,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6395</v>
+        <v>6353.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6638,26 +6638,26 @@
         <v>0.676215852</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.458975026</v>
+        <v>0.458880775</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.337566583</v>
+        <v>0.337398374</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.24472434</v>
+        <v>0.244466541</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180949976</v>
+        <v>0.18065153</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.175563643</v>
+        <v>0.1753381</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.203768523</v>
+        <v>0.203647416</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.235960708</v>
+        <v>0.235979995</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,29 +6952,29 @@
         <v>0.150738079</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150735373</v>
+        <v>0.150745112</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150740919</v>
+        <v>0.150738916</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150748565</v>
+        <v>0.1507502</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150735794</v>
+        <v>0.150754453</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150736372</v>
+        <v>0.150738393</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150749569</v>
+        <v>0.150748868</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150743303</v>
+        <v>0.150748234</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8289,36 +8289,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.000140259</v>
+        <v>0.000487111</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.003595682</v>
+        <v>-0.003287852</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.005529952</v>
+        <v>-0.00516951</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>342.708589552</v>
+        <v>342.708951613</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.005720748</v>
+        <v>-0.00320554</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.00122944</v>
+        <v>0.001225718</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.005494363</v>
+        <v>0.007017261</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>342.705370955</v>
+        <v>342.699934474</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.000378404</v>
+        <v>0.004834092</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.002626559</v>
+        <v>-0.000504591</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8417,36 +8417,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000140259</v>
+        <v>0.000487111</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.003595682</v>
+        <v>-0.003287852</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005529952</v>
+        <v>-0.00516951</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>342.708589552</v>
+        <v>342.708951613</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.005720748</v>
+        <v>-0.00320554</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00122944</v>
+        <v>0.001225718</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.005494363</v>
+        <v>0.007017261</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>342.705370955</v>
+        <v>342.699934474</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.000378404</v>
+        <v>0.004834092</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.002626559</v>
+        <v>-0.000504591</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8683,26 +8683,26 @@
         <v>-0.600660293</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>4.329142267</v>
+        <v>4.329314502</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>-0.29423742</v>
+        <v>-0.29422791</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>-0.344964968</v>
+        <v>-0.344949171</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>-0.675545302</v>
+        <v>-0.675358266</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>5.207498384</v>
+        <v>5.20456503</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>-0.356277552</v>
+        <v>-0.356181023</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>-0.458074953</v>
+        <v>-0.457872891</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8811,26 +8811,26 @@
         <v>0.2720476</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>-0.615540971</v>
+        <v>-0.61556546</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.5799095480000001</v>
+        <v>0.57994649</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.30371326</v>
+        <v>0.303725506</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.298831024</v>
+        <v>0.298778413</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.575442272</v>
+        <v>-0.575531003</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.575626718</v>
+        <v>0.575732077</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.302366969</v>
+        <v>0.302395956</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>6410</v>
+        <v>6270</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2194294282444856</v>
+        <v>0.2194270155084646</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08583635333701876</v>
+        <v>0.08583747625169227</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03675920008769111</v>
+        <v>0.036758551296326</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03520331843032391</v>
+        <v>0.03520159371307514</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34014,7 +34014,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39403,7 +39403,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41631,7 +41631,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.11</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -41641,7 +41641,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -41681,7 +41681,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.88</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 253964억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 253950억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 263123억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 263087억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 272040억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 271982억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283133억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283054억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 298498억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 298412억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 316710억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 316627억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 336233억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 336153억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1722,43 +1722,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 253964억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 253950억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 263123억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 263087억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 272040억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 271982억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283133억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283054억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 298498억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 298412억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 316710억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 316627억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 336233억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 336153억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4364,7 +4364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5235,35 +5235,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5354,35 +5354,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5592,35 +5592,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5711,35 +5711,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5830,35 +5830,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5949,35 +5949,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6068,35 +6068,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6203,7 +6203,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6270</v>
+        <v>6170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6476,7 +6476,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6353.3</v>
+        <v>6325</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6638,26 +6638,26 @@
         <v>0.676215852</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.458880775</v>
+        <v>0.458786524</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.337398374</v>
+        <v>0.337202131</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.244466541</v>
+        <v>0.244208743</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.18065153</v>
+        <v>0.180330127</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.1753381</v>
+        <v>0.175090991</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.203647416</v>
+        <v>0.203509581</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.235979995</v>
+        <v>0.23594009</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,29 +6952,29 @@
         <v>0.150738079</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150745112</v>
+        <v>0.150754851</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150738916</v>
+        <v>0.150740073</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.1507502</v>
+        <v>0.150751835</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150754453</v>
+        <v>0.150737153</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150738393</v>
+        <v>0.150743178</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150748868</v>
+        <v>0.150753419</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150748234</v>
+        <v>0.150736439</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8289,36 +8289,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.000487111</v>
+        <v>-0.000612976</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.003287852</v>
+        <v>-0.004205879</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.00516951</v>
+        <v>-0.006429876</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>342.708951613</v>
+        <v>342.707633887</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.00320554</v>
+        <v>-0.002364863</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.001225718</v>
+        <v>0.002290437</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.007017261</v>
+        <v>-0.007968998999999999</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>342.699934474</v>
+        <v>342.712548167</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.004834092</v>
+        <v>-0.002692962</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.000504591</v>
+        <v>-0.007913737000000001</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8417,36 +8417,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000487111</v>
+        <v>-0.000612976</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.003287852</v>
+        <v>-0.004205879</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.00516951</v>
+        <v>-0.006429876</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>342.708951613</v>
+        <v>342.707633887</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.00320554</v>
+        <v>-0.002364863</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.001225718</v>
+        <v>0.002290437</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.007017261</v>
+        <v>-0.007968998999999999</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>342.699934474</v>
+        <v>342.712548167</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.004834092</v>
+        <v>-0.002692962</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000504591</v>
+        <v>-0.007913737000000001</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8686,23 +8686,23 @@
         <v>4.329314502</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>-0.29422791</v>
+        <v>-0.294195592</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>-0.344949171</v>
+        <v>-0.344887586</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>-0.675358266</v>
+        <v>-0.675124065</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>5.20456503</v>
+        <v>5.200301205</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>-0.356181023</v>
+        <v>-0.356015129</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>-0.457872891</v>
+        <v>-0.457621639</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8814,23 +8814,23 @@
         <v>-0.61556546</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.57994649</v>
+        <v>0.579882788</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.303725506</v>
+        <v>0.303697432</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.298778413</v>
+        <v>0.298735039</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.575531003</v>
+        <v>-0.57560964</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.575732077</v>
+        <v>0.575725268</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.302395956</v>
+        <v>0.302446494</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9493,11 +9493,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>6270</v>
+        <v>6170</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,170원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,460원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2194270155084646</v>
+        <v>0.2194409637603228</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08583747625169227</v>
+        <v>0.08583541555728504</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.036758551296326</v>
+        <v>0.03675940546920786</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03520159371307514</v>
+        <v>0.03520052410911566</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34014,7 +34014,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39403,7 +39403,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41631,7 +41631,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.890000000000001</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="32">
@@ -41641,7 +41641,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="33">
@@ -41681,7 +41681,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.67</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -4364,7 +4364,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 253950억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 253942억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 263087억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 263078억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 271982억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 271973억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283054억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283044억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 298412억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 298410억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 316627억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 316625억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 336153억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 336152억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1722,43 +1722,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 253950억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 253942억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 263087억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 263078억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 271982억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 271973억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283054억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283044억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 298412억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 298410억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 316627억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 316625억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 336153억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 336152억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5235,35 +5235,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5354,35 +5354,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5592,35 +5592,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5711,35 +5711,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5830,35 +5830,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5949,35 +5949,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6068,35 +6068,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6203,7 +6203,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>6170</v>
+        <v>5940</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6385,7 +6385,7 @@
         <v>5480</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>6020</v>
+        <v>5850</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6476,7 +6476,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6325</v>
+        <v>6232</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6638,26 +6638,26 @@
         <v>0.676215852</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.458786524</v>
+        <v>0.458755107</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.337202131</v>
+        <v>0.337174096</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.244208743</v>
+        <v>0.244171915</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180330127</v>
+        <v>0.180284212</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.175090991</v>
+        <v>0.175094762</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.203509581</v>
+        <v>0.203534814</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.23594009</v>
+        <v>0.235976675</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6952,23 +6952,23 @@
         <v>0.150738079</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150754851</v>
+        <v>0.150736561</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150740073</v>
+        <v>0.150743233</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150751835</v>
+        <v>0.150756298</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150737153</v>
+        <v>0.150743017</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150743178</v>
+        <v>0.15074594</v>
       </c>
       <c r="AM23" s="24" t="n">
         <v>0.150753419</v>
@@ -8289,36 +8289,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.000612976</v>
+        <v>-0.000974709</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.004205879</v>
+        <v>-0.004518767</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.006429876</v>
+        <v>-0.006855778</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>342.707633887</v>
+        <v>342.709376014</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.002364863</v>
+        <v>-0.002803545</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.002290437</v>
+        <v>-0.008065096000000001</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.007968998999999999</v>
+        <v>0.001481924</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>342.712548167</v>
+        <v>342.712041417</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.002692962</v>
+        <v>-0.003268464</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.007913737000000001</v>
+        <v>-0.00832431</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8417,36 +8417,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.000612976</v>
+        <v>-0.000974709</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.004205879</v>
+        <v>-0.004518767</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.006429876</v>
+        <v>-0.006855778</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>342.707633887</v>
+        <v>342.709376014</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002364863</v>
+        <v>-0.002803545</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.002290437</v>
+        <v>-0.008065096000000001</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.007968998999999999</v>
+        <v>0.001481924</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>342.712548167</v>
+        <v>342.712041417</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.002692962</v>
+        <v>-0.003268464</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.007913737000000001</v>
+        <v>-0.00832431</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8689,20 +8689,20 @@
         <v>-0.294195592</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>-0.344887586</v>
+        <v>-0.344841797</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>-0.675124065</v>
+        <v>-0.675146771</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>5.200301205</v>
+        <v>5.200516351</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>-0.356015129</v>
+        <v>-0.356037474</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>-0.457621639</v>
+        <v>-0.457567757</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8817,20 +8817,20 @@
         <v>0.579882788</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.303697432</v>
+        <v>0.303657111</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.298735039</v>
+        <v>0.298775207</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>-0.57560964</v>
+        <v>-0.575633454</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.575725268</v>
+        <v>0.575813692</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.302446494</v>
+        <v>0.302410883</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9493,11 +9493,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>6170</v>
+        <v>5940</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,460원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,250원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2194409637603228</v>
+        <v>0.2194452940770194</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08583541555728504</v>
+        <v>0.08583431187816888</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03675940546920786</v>
+        <v>0.03675915986836449</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03520052410911566</v>
+        <v>0.03520022079859599</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39403,7 +39403,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41631,7 +41631,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.73</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -41641,7 +41641,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="33">
@@ -41681,7 +41681,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.51</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 255228억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 255226억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 264589억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 264609억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 273339억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 273380억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283443억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283505억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 297493억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 297576억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 314813억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 314894억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 333844억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 333921억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 255228억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255226억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 264589억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 264609억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 273339억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 273380억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283443억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283505억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 297493억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 297576억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 314813억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 314894억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 333844억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 333921억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5420,35 +5420,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5539,35 +5539,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5658,35 +5658,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5777,35 +5777,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5896,35 +5896,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6015,35 +6015,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6134,35 +6134,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6253,35 +6253,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6826,23 +6826,23 @@
         <v>0.466138107</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.344855621</v>
+        <v>0.344939725</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.250432733</v>
+        <v>0.250616875</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.179202932</v>
+        <v>0.179454879</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.165598817</v>
+        <v>0.165920243</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.189823018</v>
+        <v>0.190040439</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.221335375</v>
+        <v>0.221450027</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7140,26 +7140,26 @@
         <v>0.150748923</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150736904</v>
+        <v>0.150748322</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150737785</v>
+        <v>0.150745038</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150745863</v>
+        <v>0.1507525</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.15074915</v>
+        <v>0.150744348</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150743732</v>
+        <v>0.150741798</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150742741</v>
+        <v>0.150754617</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8629,36 +8629,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000672718</v>
+        <v>5.5566e-05</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007143622</v>
+        <v>-0.007705139</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.003953042</v>
+        <v>-0.004736809</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>68.537960123</v>
+        <v>68.537096547</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.008932280000000001</v>
+        <v>-0.002018439</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00068497</v>
+        <v>-0.003661359</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.001455195</v>
+        <v>-0.006806689</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>68.536862777</v>
+        <v>68.54148508199999</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.003256579</v>
+        <v>-0.008566722000000001</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.005398173</v>
+        <v>-0.000470494</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8757,36 +8757,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.000672718</v>
+        <v>5.5566e-05</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.007143622</v>
+        <v>-0.007705139</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.003953042</v>
+        <v>-0.004736809</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>68.537960123</v>
+        <v>68.537096547</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.008932280000000001</v>
+        <v>-0.002018439</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.00068497</v>
+        <v>-0.003661359</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.001455195</v>
+        <v>-0.006806689</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>68.536862777</v>
+        <v>68.54148508199999</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.003256579</v>
+        <v>-0.008566722000000001</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.005398173</v>
+        <v>-0.000470494</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -9026,23 +9026,23 @@
         <v>-0.553804119</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-4.549693829</v>
+        <v>-4.550164861</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>1.070329087</v>
+        <v>1.070187077</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.652159979</v>
+        <v>0.652182273</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.144392288</v>
+        <v>0.144497459</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.370012543</v>
+        <v>0.369949837</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.226183996</v>
+        <v>0.226205497</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9157,20 +9157,20 @@
         <v>0.088371455</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.067796468</v>
+        <v>0.067804874</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.080110845</v>
+        <v>0.080118087</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.02712828</v>
+        <v>0.027142461</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.07744709800000001</v>
+        <v>0.07745909199999999</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.060203114</v>
+        <v>0.060207321</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,150원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2194352700376797</v>
+        <v>0.2194427647797572</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.08583656808449641</v>
+        <v>0.08583661694983119</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02979412333040863</v>
+        <v>0.02979182662342874</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.03515558217411637</v>
+        <v>0.0351506885446606</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 255226억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 255224억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 264609억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 264597억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 273380억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 273359억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283505억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283476억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 297576억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 297542억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 314894억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 314861억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 333921억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 333890억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 255226억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255224억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 264609억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 264597억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 273380억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 273359억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283505억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283476억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 297576억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 297542억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 314894억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 314861억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 333921억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 333890억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4549,7 +4549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5420,35 +5420,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5539,35 +5539,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5658,35 +5658,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5777,35 +5777,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5896,35 +5896,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6015,35 +6015,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6134,35 +6134,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6253,35 +6253,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6823,26 +6823,26 @@
         <v>0.680102484</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.466138107</v>
+        <v>0.46610669</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.344939725</v>
+        <v>0.344883656</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.250616875</v>
+        <v>0.25050639</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.179454879</v>
+        <v>0.179340357</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.165920243</v>
+        <v>0.165816655</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.190040439</v>
+        <v>0.18996498</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.221450027</v>
+        <v>0.221440141</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7137,29 +7137,29 @@
         <v>0.150732936</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150748923</v>
+        <v>0.150752154</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150748322</v>
+        <v>0.150754607</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150745038</v>
+        <v>0.150758357</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.1507525</v>
+        <v>0.150747718</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150744348</v>
+        <v>0.150742592</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150741798</v>
+        <v>0.150740124</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150754617</v>
+        <v>0.150745045</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8629,36 +8629,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>5.5566e-05</v>
+        <v>0.000131053</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007705139</v>
+        <v>-0.007629578</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004736809</v>
+        <v>-0.004620021</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>68.537096547</v>
+        <v>68.537235274</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002018439</v>
+        <v>-0.00187282</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.003661359</v>
+        <v>0.006477844</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.006806689</v>
+        <v>-0.00442834</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>68.54148508199999</v>
+        <v>68.53382882299999</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.008566722000000001</v>
+        <v>-0.006269846</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.000470494</v>
+        <v>-0.008180522000000001</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8757,36 +8757,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>5.5566e-05</v>
+        <v>0.000131053</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.007705139</v>
+        <v>-0.007629578</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.004736809</v>
+        <v>-0.004620021</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>68.537096547</v>
+        <v>68.537235274</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.002018439</v>
+        <v>-0.00187282</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.003661359</v>
+        <v>0.006477844</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.006806689</v>
+        <v>-0.00442834</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>68.54148508199999</v>
+        <v>68.53382882299999</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.008566722000000001</v>
+        <v>-0.006269846</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.000470494</v>
+        <v>-0.008180522000000001</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -9026,23 +9026,23 @@
         <v>-0.553804119</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-4.550164861</v>
+        <v>-4.549693829</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>1.070187077</v>
+        <v>1.070329087</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.652182273</v>
+        <v>0.652224074</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.144497459</v>
+        <v>0.144464272</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.369949837</v>
+        <v>0.369974917</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.226205497</v>
+        <v>0.226167207</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9161,16 +9161,16 @@
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.080118087</v>
+        <v>0.080110215</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.027142461</v>
+        <v>0.027135371</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.07745909199999999</v>
+        <v>0.077460191</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.060207321</v>
+        <v>0.060201528</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2194427647797572</v>
+        <v>0.2194416276711539</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.08583661694983119</v>
+        <v>0.08584188984117089</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02979182662342874</v>
+        <v>0.02979271686685315</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.0351506885446606</v>
+        <v>0.03515258790829119</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -4549,7 +4549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -4549,7 +4549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5940</v>
+        <v>5750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6570,7 +6570,7 @@
         <v>5480</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5850</v>
+        <v>5640</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6661,7 +6661,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6232</v>
+        <v>6151.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>5940</v>
+        <v>5750</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40047,7 +40047,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42319,7 +42319,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.93</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="32">
@@ -42329,7 +42329,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33">
@@ -42369,7 +42369,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.14</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 255224억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 255216억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 264597억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 264551억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 273359억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 273274억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283476억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283347억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 297542억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 297378억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 314861억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 314695억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 333890억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 333725억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 255224억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255216억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 264597억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 264551억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 273359억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 273274억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283476억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283347억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 297542억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 297378억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 314861억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 314695억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 333890억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 333725억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4549,7 +4549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5420,35 +5420,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5539,35 +5539,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5658,35 +5658,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5777,35 +5777,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5896,35 +5896,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6015,35 +6015,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6134,35 +6134,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6253,35 +6253,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6388,7 +6388,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5750</v>
+        <v>5650</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6570,7 +6570,7 @@
         <v>5480</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>5640</v>
+        <v>5290</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6661,7 +6661,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6151.7</v>
+        <v>6084.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6823,26 +6823,26 @@
         <v>0.680102484</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.46610669</v>
+        <v>0.466075273</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.344883656</v>
+        <v>0.344659378</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.25050639</v>
+        <v>0.250138106</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.179340357</v>
+        <v>0.178813559</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.165816655</v>
+        <v>0.165198757</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.18996498</v>
+        <v>0.189537987</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.221440141</v>
+        <v>0.221181323</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7137,29 +7137,29 @@
         <v>0.150732936</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150752154</v>
+        <v>0.150733955</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150754607</v>
+        <v>0.150738054</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150758357</v>
+        <v>0.15074385</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150747718</v>
+        <v>0.150737366</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150742592</v>
+        <v>0.150752198</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150740124</v>
+        <v>0.150749277</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150745045</v>
+        <v>0.150749041</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8629,36 +8629,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.000131053</v>
+        <v>-0.000361343</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007629578</v>
+        <v>-0.007998541</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004620021</v>
+        <v>-0.005011163</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>68.537235274</v>
+        <v>68.529108902</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.00187282</v>
+        <v>-0.007786498</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.006477844</v>
+        <v>0.000674446</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.00442834</v>
+        <v>-0.005977346</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>68.53382882299999</v>
+        <v>68.542245028</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.006269846</v>
+        <v>-0.008007247</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.008180522000000001</v>
+        <v>-0.002213806</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8757,36 +8757,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.000131053</v>
+        <v>-0.000361343</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.007629578</v>
+        <v>-0.007998541</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.004620021</v>
+        <v>-0.005011163</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>68.537235274</v>
+        <v>68.529108902</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.00187282</v>
+        <v>-0.007786498</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.006477844</v>
+        <v>0.000674446</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.00442834</v>
+        <v>-0.005977346</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>68.53382882299999</v>
+        <v>68.542245028</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.006269846</v>
+        <v>-0.008007247</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.008180522000000001</v>
+        <v>-0.002213806</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -9026,23 +9026,23 @@
         <v>-0.553804119</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-4.549693829</v>
+        <v>-4.549222798</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>1.070329087</v>
+        <v>1.070338421</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.652224074</v>
+        <v>0.652115385</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.144464272</v>
+        <v>0.144337097</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.369974917</v>
+        <v>0.369952192</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.226167207</v>
+        <v>0.226215226</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9154,23 +9154,23 @@
         <v>0.024703511</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.088371455</v>
+        <v>0.088362306</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.067804874</v>
+        <v>0.067788631</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.080110215</v>
+        <v>0.080096361</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.027135371</v>
+        <v>0.027114493</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.077460191</v>
+        <v>0.077429107</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.060201528</v>
+        <v>0.06019351</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9833,11 +9833,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>5750</v>
+        <v>5650</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 6,150원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,950원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2194416276711539</v>
+        <v>0.2194452456941873</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.08584188984117089</v>
+        <v>0.0858363335958089</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02979271686685315</v>
+        <v>0.02979775207756735</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.03515258790829119</v>
+        <v>0.03516322044571674</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40047,7 +40047,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42319,7 +42319,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.65</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="32">
@@ -42329,7 +42329,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="33">
@@ -42369,7 +42369,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.85</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 255216억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 255215억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 264551억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 264588억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 273274억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 273348억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283347억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283457억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 297378억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 297524억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 314695억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 314836억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 333725억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 333860억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 255216억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255215억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 264551억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 264588억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 273274억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 273348억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283347억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283457억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 297378억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 297524억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 314695억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 314836억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 333725억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 333860억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4549,7 +4549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5420,35 +5420,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5539,35 +5539,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5658,35 +5658,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5777,35 +5777,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5896,35 +5896,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6015,35 +6015,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6134,35 +6134,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6253,35 +6253,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6388,7 +6388,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5650</v>
+        <v>5680</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6661,7 +6661,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6084.3</v>
+        <v>6031.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6823,26 +6823,26 @@
         <v>0.680102484</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.466075273</v>
+        <v>0.466043856</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.344659378</v>
+        <v>0.344855621</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.250138106</v>
+        <v>0.250469561</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.178813559</v>
+        <v>0.179271645</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.165198757</v>
+        <v>0.165780902</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.189537987</v>
+        <v>0.189906402</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.221181323</v>
+        <v>0.221358308</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7137,29 +7137,29 @@
         <v>0.150732936</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150733955</v>
+        <v>0.150737185</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150738054</v>
+        <v>0.150736904</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.15074385</v>
+        <v>0.150733345</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150737366</v>
+        <v>0.150737079</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150752198</v>
+        <v>0.150753676</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150749277</v>
+        <v>0.150750688</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150749041</v>
+        <v>0.150735471</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8629,36 +8629,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.000361343</v>
+        <v>2.3486e-05</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007998541</v>
+        <v>-0.007713449</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005011163</v>
+        <v>-0.004715746</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>68.529108902</v>
+        <v>68.52934335899999</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.007786498</v>
+        <v>0.000237679</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.000674446</v>
+        <v>-0.01137831</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.005977346</v>
+        <v>-0.002354354</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>68.542245028</v>
+        <v>68.53371971999999</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.008007247</v>
+        <v>0.003623313</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.002213806</v>
+        <v>-0.016113863</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8757,36 +8757,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.000361343</v>
+        <v>2.3486e-05</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.007998541</v>
+        <v>-0.007713449</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.005011163</v>
+        <v>-0.004715746</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>68.529108902</v>
+        <v>68.52934335899999</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.007786498</v>
+        <v>0.000237679</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.000674446</v>
+        <v>-0.01137831</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.005977346</v>
+        <v>-0.002354354</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>68.542245028</v>
+        <v>68.53371971999999</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.008007247</v>
+        <v>0.003623313</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.002213806</v>
+        <v>-0.016113863</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -9026,23 +9026,23 @@
         <v>-0.553804119</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-4.549222798</v>
+        <v>-4.549693829</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>1.070338421</v>
+        <v>1.070196391</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.652115385</v>
+        <v>0.65226588</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.144337097</v>
+        <v>0.144431082</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.369952192</v>
+        <v>0.37</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.226215226</v>
+        <v>0.226178399</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9154,23 +9154,23 @@
         <v>0.024703511</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.088362306</v>
+        <v>0.088371455</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.067788631</v>
+        <v>0.067796468</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.080096361</v>
+        <v>0.080110845</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.027114493</v>
+        <v>0.027135569</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.077429107</v>
+        <v>0.077453645</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.06019351</v>
+        <v>0.060202321</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9833,11 +9833,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>5650</v>
+        <v>5680</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,700원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2194452456941873</v>
+        <v>0.2194425320506857</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0858363335958089</v>
+        <v>0.08583422447725877</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02979775207756735</v>
+        <v>0.02979352007998413</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.03516322044571674</v>
+        <v>0.03515427034908726</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40047,7 +40047,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42319,7 +42319,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.5</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -42369,7 +42369,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.69</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 255215억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 255574억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 264588억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 265188억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 273348억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 273966억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283457억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 283920억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 297524억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 297343억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 314836억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 314042억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 333860억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 332644억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 255215억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255574억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 264588억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 265188억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 273348억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 273966억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283457억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 283920억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 297524억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 297343억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 314836억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 314042억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 333860억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 332644억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2160,7 +2160,7 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1270억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1271억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2172,13 +2172,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1409억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1410억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1518억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1519억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2220,7 +2220,7 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1270억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1271억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2232,13 +2232,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1409억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1410억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1518억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1519억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4549,7 +4549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5420,35 +5420,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5539,35 +5539,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5658,35 +5658,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5777,35 +5777,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5896,35 +5896,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6015,35 +6015,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6134,35 +6134,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6253,35 +6253,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6388,7 +6388,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5680</v>
+        <v>5750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6661,7 +6661,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>6031.2</v>
+        <v>5907.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6823,26 +6823,26 @@
         <v>0.680102484</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.466043856</v>
+        <v>0.468117379</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.344855621</v>
+        <v>0.347883375</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.250469561</v>
+        <v>0.253305344</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.179271645</v>
+        <v>0.181195602</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.165780902</v>
+        <v>0.163428205</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.189906402</v>
+        <v>0.184238441</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.221358308</v>
+        <v>0.21415768</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7137,29 +7137,29 @@
         <v>0.150732936</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150737185</v>
+        <v>0.150738284</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150736904</v>
+        <v>0.150751888</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150733345</v>
+        <v>0.150744909</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150737079</v>
+        <v>0.150743635</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150753676</v>
+        <v>0.150753214</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150750688</v>
+        <v>0.150745561</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.150735471</v>
+        <v>0.15075389</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8629,36 +8629,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>2.3486e-05</v>
+        <v>-0.000622526</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007713449</v>
+        <v>-0.007685105</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004715746</v>
+        <v>-0.004134256</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>68.52934335899999</v>
+        <v>68.53871941600001</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.000237679</v>
+        <v>-0.005068052</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.01137831</v>
+        <v>-0.004198026</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.002354354</v>
+        <v>0.003844235</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>68.53371971999999</v>
+        <v>68.540828846</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.003623313</v>
+        <v>-0.00189491</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.016113863</v>
+        <v>0.008299084999999999</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8757,36 +8757,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>2.3486e-05</v>
+        <v>-0.000622526</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.007713449</v>
+        <v>-0.007685105</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.004715746</v>
+        <v>-0.004134256</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>68.52934335899999</v>
+        <v>68.53871941600001</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.000237679</v>
+        <v>-0.005068052</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.01137831</v>
+        <v>-0.004198026</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>-0.002354354</v>
+        <v>0.003844235</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>68.53371971999999</v>
+        <v>68.540828846</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.003623313</v>
+        <v>-0.00189491</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>-0.016113863</v>
+        <v>0.008299084999999999</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -9023,26 +9023,26 @@
         <v>-0.656238711</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>-0.553804119</v>
+        <v>-0.555485498</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-4.549693829</v>
+        <v>-4.572576832</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>1.070196391</v>
+        <v>1.068687136</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.65226588</v>
+        <v>0.6516537650000001</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.144431082</v>
+        <v>0.144052369</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.37</v>
+        <v>0.368973456</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.226178399</v>
+        <v>0.225651679</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9151,26 +9151,26 @@
         <v>0.093091893</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.024703511</v>
+        <v>0.024778512</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.088371455</v>
+        <v>0.08847476899999999</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.067796468</v>
+        <v>0.06786912</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.080110845</v>
+        <v>0.080170636</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.027135569</v>
+        <v>0.027098514</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.077453645</v>
+        <v>0.07731326099999999</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.060202321</v>
+        <v>0.060082841</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9833,11 +9833,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>5680</v>
+        <v>5750</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,460원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2194425320506857</v>
+        <v>0.2194436691785283</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.08583422447725877</v>
+        <v>0.08583968310668301</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02979352007998413</v>
+        <v>0.0298355356888378</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.03515427034908726</v>
+        <v>0.03523446702544443</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40047,7 +40047,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42299,7 +42299,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>665</v>
+        <v>665.1</v>
       </c>
     </row>
     <row r="30">
@@ -42319,7 +42319,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.539999999999999</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="32">
@@ -42329,7 +42329,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33">
@@ -42369,7 +42369,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.74</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/101930_model.xlsx
+++ b/argus/kship/models/101930_model.xlsx
@@ -675,43 +675,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 255574억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 255852억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 265188억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 265700억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 273966억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 274541억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 283920억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 284424억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 297343억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 297400억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 314042억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 313630억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−2) 332644억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−2) 331909억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1782,43 +1782,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 255574억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 255852억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 265188억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 265700억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 273966억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 274541억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 283920억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 284424억 × 비례계수 0.0067 × 계절비중 Q1 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 297343억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 297400억 × 비례계수 0.0067 × 계절비중 Q2 0.273(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 314042억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 313630억 × 비례계수 0.0067 × 계절비중 Q3 0.271(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−2) 332644억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−2) 331909억 × 비례계수 0.0067 × 계절비중 Q4 0.185(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.88, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2166,7 +2166,7 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1372억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q2~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1373억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2226,7 +2226,7 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1372억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1373억 × 2.98%(주석 이자수익 ÷ 평균 이자발생자산(2025Q2~2026Q2)) − 총차입금 466억 × 3.52%(주석 이자비용 ÷ 평균 총차입금(2025Q2~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4549,7 +4549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5420,35 +5420,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5539,35 +5539,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5658,35 +5658,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5777,35 +5777,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5896,35 +5896,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6015,35 +6015,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6134,35 +6134,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6253,35 +6253,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6388,7 +6388,7 @@
         <v>6210</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>5750</v>
+        <v>6340</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6661,7 +6661,7 @@
         <v>6807.6</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>5907.3</v>
+        <v>5925</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6823,26 +6823,26 @@
         <v>0.680102484</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.468117379</v>
+        <v>0.469719647</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.347883375</v>
+        <v>0.350490608</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.253305344</v>
+        <v>0.255920156</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.181195602</v>
+        <v>0.183302794</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.163428205</v>
+        <v>0.162394989</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.184238441</v>
+        <v>0.18039525</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.21415768</v>
+        <v>0.208961351</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7137,29 +7137,29 @@
         <v>0.150732936</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.150738284</v>
+        <v>0.150744961</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.150751888</v>
+        <v>0.150751474</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.150744909</v>
+        <v>0.150753621</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.150743635</v>
+        <v>0.150746182</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.150753214</v>
+        <v>0.150741109</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.150745561</v>
+        <v>0.150750941</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.15075389</v>
+        <v>0.150747065</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8629,36 +8629,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.000622526</v>
+        <v>-0.000809684</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.007685105</v>
+        <v>-0.007846888</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004134256</v>
+        <v>-0.004257786</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>68.53871941600001</v>
+        <v>68.541077503</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.005068052</v>
+        <v>-0.005516347</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.004198026</v>
+        <v>0.002605387</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.003844235</v>
+        <v>-0.005427026</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>68.540828846</v>
+        <v>68.540767004</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.00189491</v>
+        <v>0.004508613</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.008299084999999999</v>
+        <v>0.000793615</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8757,36 +8757,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>-0.000622526</v>
+        <v>-0.000809684</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>-0.007685105</v>
+        <v>-0.007846888</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>-0.004134256</v>
+        <v>-0.004257786</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>68.53871941600001</v>
+        <v>68.541077503</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>-0.005068052</v>
+        <v>-0.005516347</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>-0.004198026</v>
+        <v>0.002605387</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.003844235</v>
+        <v>-0.005427026</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>68.540828846</v>
+        <v>68.540767004</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>-0.00189491</v>
+        <v>0.004508613</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.008299084999999999</v>
+        <v>0.000793615</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -9023,26 +9023,26 @@
         <v>-0.656238711</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>-0.555485498</v>
+        <v>-0.556746532</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>-4.572576832</v>
+        <v>-4.590801328</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>1.068687136</v>
+        <v>1.067476561</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.6516537650000001</v>
+        <v>0.651210321</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.144052369</v>
+        <v>0.143929138</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.368973456</v>
+        <v>0.368195036</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.225651679</v>
+        <v>0.225242814</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9151,26 +9151,26 @@
         <v>0.093091893</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.024778512</v>
+        <v>0.024834763</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.08847476899999999</v>
+        <v>0.08857054</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.06786912</v>
+        <v>0.067926653</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.080170636</v>
+        <v>0.08024142500000001</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.027098514</v>
+        <v>0.027105976</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.07731326099999999</v>
+        <v>0.077228594</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.060082841</v>
+        <v>0.059998947</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9833,11 +9833,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>5750</v>
+        <v>6340</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,460원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 5,810원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2194436691785283</v>
+        <v>0.2194432301210087</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.08583968310668301</v>
+        <v>0.08583502589447972</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.0298355356888378</v>
+        <v>0.0298374917741083</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.03523446702544443</v>
+        <v>0.03524042652735362</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40047,7 +40047,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42299,7 +42299,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>665.1</v>
+        <v>665.3</v>
       </c>
     </row>
     <row r="30">
@@ -42319,7 +42319,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8.65</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -42329,7 +42329,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="33">
@@ -42339,7 +42339,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0856</v>
       </c>
     </row>
     <row r="34">
@@ -42369,7 +42369,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.84</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="37">
